--- a/liste groupe 1bis.xlsx
+++ b/liste groupe 1bis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC75E3A-A161-4C9C-96B4-2E86183BAEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B1B333-D4C5-46E8-A5A4-5C277AABA17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -173,6 +173,21 @@
   </si>
   <si>
     <t>03/09/2025</t>
+  </si>
+  <si>
+    <t>toto</t>
+  </si>
+  <si>
+    <t>tutu</t>
+  </si>
+  <si>
+    <t>15/09/2022</t>
+  </si>
+  <si>
+    <t>Suède</t>
+  </si>
+  <si>
+    <t>20/09/2025</t>
   </si>
 </sst>
 </file>
@@ -945,16 +960,30 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>10</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="3"/>
+      <c r="B13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A14" s="6">

--- a/liste groupe 1bis.xlsx
+++ b/liste groupe 1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B1B333-D4C5-46E8-A5A4-5C277AABA17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C165EB-4D48-4AFB-AD6C-A8377CB498E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -188,6 +188,15 @@
   </si>
   <si>
     <t>20/09/2025</t>
+  </si>
+  <si>
+    <t>coco</t>
+  </si>
+  <si>
+    <t>lulu</t>
+  </si>
+  <si>
+    <t>Finlande</t>
   </si>
 </sst>
 </file>
@@ -986,16 +995,30 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A14" s="6">
+      <c r="A14" s="5">
         <v>11</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="3"/>
+      <c r="B14" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A15" s="6">

--- a/liste groupe 1bis.xlsx
+++ b/liste groupe 1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C165EB-4D48-4AFB-AD6C-A8377CB498E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C2F1F9-E224-4CF0-95CC-E4CE569F237E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -173,30 +173,6 @@
   </si>
   <si>
     <t>03/09/2025</t>
-  </si>
-  <si>
-    <t>toto</t>
-  </si>
-  <si>
-    <t>tutu</t>
-  </si>
-  <si>
-    <t>15/09/2022</t>
-  </si>
-  <si>
-    <t>Suède</t>
-  </si>
-  <si>
-    <t>20/09/2025</t>
-  </si>
-  <si>
-    <t>coco</t>
-  </si>
-  <si>
-    <t>lulu</t>
-  </si>
-  <si>
-    <t>Finlande</t>
   </si>
 </sst>
 </file>
@@ -969,56 +945,28 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>10</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>11</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A15" s="6">

--- a/liste groupe 1bis.xlsx
+++ b/liste groupe 1bis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C2F1F9-E224-4CF0-95CC-E4CE569F237E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFBE67A-5C0D-447F-A88A-1105CA725845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 1bis.xlsx
+++ b/liste groupe 1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFBE67A-5C0D-447F-A88A-1105CA725845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CC8648-67AB-4067-AD52-7FA9ACF4D4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 1bis.xlsx
+++ b/liste groupe 1bis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CC8648-67AB-4067-AD52-7FA9ACF4D4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD102D6-53EC-49A9-A4EF-712DA1703DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/liste groupe 1bis.xlsx
+++ b/liste groupe 1bis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\VERO\ASTI\TDB_ASTI\EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD102D6-53EC-49A9-A4EF-712DA1703DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADA1CDA-2706-46EE-A9E7-2F3F26499FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6960" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
